--- a/outputs/tables/tab5_fiscal.xlsx
+++ b/outputs/tables/tab5_fiscal.xlsx
@@ -6,44 +6,44 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
-  <si>
-    <t xml:space="preserve">Tabla 5. Subsidio, costo del choque y espacio fiscal por país (2022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">País</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subsidio
-(% PIB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cambio
-2021-22 (pp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costo choque
-(USD mil mill.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deuda
-(% PIB)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+  <si>
+    <t xml:space="preserve">Table 5. Subsidy, illustrative shock cost, and fiscal space by country (2022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsidy
+(% of GDP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change
+2021–22 (pp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative cost
+(USD billion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt
+(% of GDP)</t>
   </si>
   <si>
     <t xml:space="preserve">Balance
-(% PIB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuadrante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel A. Exportadores netos</t>
+(% of GDP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadrant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel A. Net oil exporters</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">−5.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Reforma urgente</t>
+    <t xml:space="preserve">Urgent reform</t>
   </si>
   <si>
     <t xml:space="preserve">  Bolivia</t>
@@ -103,13 +103,13 @@
     <t xml:space="preserve">57.2</t>
   </si>
   <si>
-    <t xml:space="preserve">+0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reforma gradual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Trinidad y Tobago</t>
+    <t xml:space="preserve">0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gradual reform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Trinidad and Tobago</t>
   </si>
   <si>
     <t xml:space="preserve">3.19</t>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">−6.4</t>
   </si>
   <si>
-    <t xml:space="preserve">  México</t>
+    <t xml:space="preserve">  Mexico</t>
   </si>
   <si>
     <t xml:space="preserve">1.64</t>
@@ -172,36 +172,39 @@
     <t xml:space="preserve">−0.28</t>
   </si>
   <si>
+    <t xml:space="preserve">0.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No immediate pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  N (countries)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel B. Net oil importers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Suriname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3.78</t>
+  </si>
+  <si>
     <t xml:space="preserve">n.a.</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin presión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  N (países)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel B. Importadores netos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Surinam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3.78</t>
-  </si>
-  <si>
     <t xml:space="preserve">111.7</t>
   </si>
   <si>
@@ -223,7 +226,7 @@
     <t xml:space="preserve">−3.8</t>
   </si>
   <si>
-    <t xml:space="preserve">  Haití</t>
+    <t xml:space="preserve">  Haiti</t>
   </si>
   <si>
     <t xml:space="preserve">2.32</t>
@@ -238,7 +241,7 @@
     <t xml:space="preserve">−1.8</t>
   </si>
   <si>
-    <t xml:space="preserve">  República Dominicana</t>
+    <t xml:space="preserve">  Dominican Republic</t>
   </si>
   <si>
     <t xml:space="preserve">2.06</t>
@@ -283,7 +286,7 @@
     <t xml:space="preserve">−2.7</t>
   </si>
   <si>
-    <t xml:space="preserve">  Belice</t>
+    <t xml:space="preserve">  Belize</t>
   </si>
   <si>
     <t xml:space="preserve">0.85</t>
@@ -325,7 +328,7 @@
     <t xml:space="preserve">−7.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Vigilar</t>
+    <t xml:space="preserve">Monitor</t>
   </si>
   <si>
     <t xml:space="preserve">  Nicaragua</t>
@@ -343,7 +346,7 @@
     <t xml:space="preserve">+0.6</t>
   </si>
   <si>
-    <t xml:space="preserve">  Granada</t>
+    <t xml:space="preserve">  Grenada</t>
   </si>
   <si>
     <t xml:space="preserve">+0.10</t>
@@ -379,7 +382,7 @@
     <t xml:space="preserve">104.0</t>
   </si>
   <si>
-    <t xml:space="preserve">  Antigua y Barbuda</t>
+    <t xml:space="preserve">  Antigua and Barbuda</t>
   </si>
   <si>
     <t xml:space="preserve">0.33</t>
@@ -394,7 +397,7 @@
     <t xml:space="preserve">−2.9</t>
   </si>
   <si>
-    <t xml:space="preserve">  Santa Lucía</t>
+    <t xml:space="preserve">  St. Lucia</t>
   </si>
   <si>
     <t xml:space="preserve">0.22</t>
@@ -406,7 +409,7 @@
     <t xml:space="preserve">−2.5</t>
   </si>
   <si>
-    <t xml:space="preserve">  Perú</t>
+    <t xml:space="preserve">  Peru</t>
   </si>
   <si>
     <t xml:space="preserve">0.15</t>
@@ -445,7 +448,7 @@
     <t xml:space="preserve">+1.4</t>
   </si>
   <si>
-    <t xml:space="preserve">  Panamá</t>
+    <t xml:space="preserve">  Panama</t>
   </si>
   <si>
     <t xml:space="preserve">+0.01</t>
@@ -460,7 +463,7 @@
     <t xml:space="preserve">19</t>
   </si>
   <si>
-    <t xml:space="preserve">Notas. Situación fiscal de cada país con subsidio explícito relevante en 2022, ordenada por el peso del subsidio dentro de cada grupo. Sirve de respaldo a la matriz de la Figura 5: cruza cuánto pesa el subsidio con cuánto margen fiscal hay para sostenerlo. Subsidio: subsidio explícito a combustibles fósiles como porcentaje del PIB en 2022. Cambio 2021 a 2022: variación observada del subsidio de cada país entre ambos años (puntos del PIB), una medida bruta, no causal, que sí difiere entre países. Costo del choque: el efecto medio estimado para el grupo (1.79 puntos del PIB, Tabla 4) aplicado por igual al PIB de cada exportador, en miles de millones de dólares; es una valoración contrafactual del costo (cuánto representaría ese efecto promedio para cada economía), no el costo observado país por país, que es heterogéneo y se lee en la columna de cambio. Solo aplica a los exportadores netos, que es donde el modelo identifica el efecto diferencial; figura como n.a. en los importadores y en el único exportador cuyo subsidio no subió con el choque (Guyana), porque valorar un encarecimiento promedio sobre quien lo redujo contradiría su propio dato. Deuda: deuda pública bruta (% PIB). Balance: resultado fiscal del gobierno general (% PIB; signo negativo es déficit). Cuadrante: posición en la Figura 5 según las medianas de subsidio (0.81% del PIB) y deuda (64.1% del PIB) de la muestra. Reforma urgente reúne a los países por encima de ambas medianas; sin presión, a los que están por debajo de ambas. Las variables fiscales (deuda, balance) provienen del WEO del FMI y no entran en el modelo del efecto: se usan ex post para interpretar, no como controles. Fuente: IMF Fossil Fuel Subsidies Database; FMI, World Economic Outlook.</t>
+    <t xml:space="preserve">Notes. Countries with an explicit subsidy above 0.05% of GDP in 2022, sorted by subsidy within each group. Change 2021–22: observed change in the explicit subsidy (pp of GDP), descriptive. Illustrative cost: β₃ (1.79 pp of GDP, Table 3) times each net oil exporter's 2022 GDP (USD billion), an illustrative differential cost (exporters' subsidy increase beyond importers'), not the total cost of the shock; the 95% confidence interval of β₃ (−0.08 to 3.66) includes zero. n.a.: net oil importers, the comparison group. Debt: gross public debt; Balance: general government fiscal balance (negative = deficit); both % of GDP. Quadrant: position relative to the sample medians of the subsidy (0.81% of GDP) and debt (64.1% of GDP). Source: IMF Fossil Fuel Subsidies Database; IMF, World Economic Outlook.</t>
   </si>
 </sst>
 </file>
@@ -1153,13 +1156,13 @@
         <v>60</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>16</v>
@@ -1167,22 +1170,22 @@
     </row>
     <row r="14">
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
@@ -1190,22 +1193,22 @@
     </row>
     <row r="15">
       <c r="B15" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>29</v>
@@ -1213,22 +1216,22 @@
     </row>
     <row r="16">
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>29</v>
@@ -1236,22 +1239,22 @@
     </row>
     <row r="17">
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>16</v>
@@ -1259,22 +1262,22 @@
     </row>
     <row r="18">
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>16</v>
@@ -1282,22 +1285,22 @@
     </row>
     <row r="19">
       <c r="B19" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>16</v>
@@ -1305,22 +1308,22 @@
     </row>
     <row r="20">
       <c r="B20" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>54</v>
@@ -1328,45 +1331,45 @@
     </row>
     <row r="21">
       <c r="B21" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>54</v>
@@ -1374,45 +1377,45 @@
     </row>
     <row r="23">
       <c r="B23" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>54</v>
@@ -1420,91 +1423,91 @@
     </row>
     <row r="25">
       <c r="B25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="H25" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>54</v>
@@ -1512,22 +1515,22 @@
     </row>
     <row r="29">
       <c r="B29" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>54</v>
@@ -1535,22 +1538,22 @@
     </row>
     <row r="30">
       <c r="B30" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>54</v>
@@ -1558,22 +1561,22 @@
     </row>
     <row r="31">
       <c r="B31" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>54</v>
@@ -1602,9 +1605,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" ht="137.5" customHeight="1">
+    <row r="33" ht="62.5" customHeight="1">
       <c r="B33" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
